--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/140.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/140.xlsx
@@ -426,13 +426,13 @@
         <v>-5.980966370933061</v>
       </c>
       <c r="E2">
-        <v>-10.9213817111683</v>
+        <v>-9.651968934286163</v>
       </c>
       <c r="F2">
-        <v>-2.533019268060962</v>
+        <v>-2.00253609677777</v>
       </c>
       <c r="G2">
-        <v>-3.155573432155158</v>
+        <v>-1.793456091113107</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.584577783969074</v>
       </c>
       <c r="E3">
-        <v>-9.58162814752502</v>
+        <v>-9.824689461412719</v>
       </c>
       <c r="F3">
-        <v>-2.978931097722742</v>
+        <v>-2.5465233134614</v>
       </c>
       <c r="G3">
-        <v>-2.940818343022636</v>
+        <v>-1.197769768958806</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.280533364226831</v>
       </c>
       <c r="E4">
-        <v>-10.84621809958899</v>
+        <v>-10.04452423211508</v>
       </c>
       <c r="F4">
-        <v>-2.803933513676929</v>
+        <v>-2.593604403166912</v>
       </c>
       <c r="G4">
-        <v>-2.876835429385142</v>
+        <v>-1.26225588551827</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.988913794458091</v>
       </c>
       <c r="E5">
-        <v>-12.09557426509116</v>
+        <v>-11.25855377188341</v>
       </c>
       <c r="F5">
-        <v>-3.1946578502294</v>
+        <v>-2.234149279335317</v>
       </c>
       <c r="G5">
-        <v>-2.976880115581917</v>
+        <v>-1.926132824690478</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.706522171642352</v>
       </c>
       <c r="E6">
-        <v>-12.73754885431454</v>
+        <v>-11.07604721242628</v>
       </c>
       <c r="F6">
-        <v>-2.561599600192351</v>
+        <v>-2.531172008752719</v>
       </c>
       <c r="G6">
-        <v>-2.697427034975418</v>
+        <v>-2.662116756253552</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.395405004780869</v>
       </c>
       <c r="E7">
-        <v>-11.05810992688189</v>
+        <v>-11.88954681163819</v>
       </c>
       <c r="F7">
-        <v>-2.213577603254194</v>
+        <v>-1.907371592809357</v>
       </c>
       <c r="G7">
-        <v>-2.311390940732084</v>
+        <v>-1.47506768441924</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.02420457278894</v>
       </c>
       <c r="E8">
-        <v>-13.38693202701447</v>
+        <v>-12.86229925627784</v>
       </c>
       <c r="F8">
-        <v>-2.580338927578481</v>
+        <v>-2.570473900178542</v>
       </c>
       <c r="G8">
-        <v>-1.430289245455058</v>
+        <v>-0.1865768761705795</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.54988855273445</v>
       </c>
       <c r="E9">
-        <v>-13.13778897253447</v>
+        <v>-13.62729437039359</v>
       </c>
       <c r="F9">
-        <v>-3.018158436082312</v>
+        <v>-2.585446640984143</v>
       </c>
       <c r="G9">
-        <v>-0.8760608850890503</v>
+        <v>-0.7244776259369012</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.94738893322557</v>
       </c>
       <c r="E10">
-        <v>-12.70507969567954</v>
+        <v>-14.57915243596186</v>
       </c>
       <c r="F10">
-        <v>-3.17359578064582</v>
+        <v>-2.497929624878375</v>
       </c>
       <c r="G10">
-        <v>-1.199921623559333</v>
+        <v>0.3858959006623513</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.18422379965262</v>
       </c>
       <c r="E11">
-        <v>-13.86901525597502</v>
+        <v>-15.96804447106237</v>
       </c>
       <c r="F11">
-        <v>-3.062970627471557</v>
+        <v>-2.377566184516801</v>
       </c>
       <c r="G11">
-        <v>-1.588933898242472</v>
+        <v>-0.2630372359455868</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.23333093719007</v>
       </c>
       <c r="E12">
-        <v>-16.07368471271331</v>
+        <v>-15.5977149236631</v>
       </c>
       <c r="F12">
-        <v>-2.453459549226486</v>
+        <v>-2.832819513379951</v>
       </c>
       <c r="G12">
-        <v>-0.5963264081117136</v>
+        <v>0.5529096125730434</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.07412161442561</v>
       </c>
       <c r="E13">
-        <v>-14.95036503579262</v>
+        <v>-16.1146538170607</v>
       </c>
       <c r="F13">
-        <v>-3.022673866794972</v>
+        <v>-2.141483959821151</v>
       </c>
       <c r="G13">
-        <v>0.5625333684557048</v>
+        <v>1.639165814918705</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.70667545860602</v>
       </c>
       <c r="E14">
-        <v>-18.45167245514716</v>
+        <v>-17.20706665887904</v>
       </c>
       <c r="F14">
-        <v>-2.748369941766749</v>
+        <v>-2.075246045558496</v>
       </c>
       <c r="G14">
-        <v>-0.08365863644571681</v>
+        <v>1.55238317415225</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.13719662917412</v>
       </c>
       <c r="E15">
-        <v>-17.56648258391981</v>
+        <v>-18.63715875050134</v>
       </c>
       <c r="F15">
-        <v>-3.180791808273939</v>
+        <v>-2.236467879695753</v>
       </c>
       <c r="G15">
-        <v>0.906449391802892</v>
+        <v>2.312603609608329</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.38323963405859</v>
       </c>
       <c r="E16">
-        <v>-18.86747241005744</v>
+        <v>-18.57998223768049</v>
       </c>
       <c r="F16">
-        <v>-2.387106491894843</v>
+        <v>-2.136290096205598</v>
       </c>
       <c r="G16">
-        <v>0.05310662087265447</v>
+        <v>2.459687837372608</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.472194393444223</v>
       </c>
       <c r="E17">
-        <v>-19.35516188983949</v>
+        <v>-18.79576855261999</v>
       </c>
       <c r="F17">
-        <v>-2.67746997576114</v>
+        <v>-2.063808776828044</v>
       </c>
       <c r="G17">
-        <v>2.710928448893438</v>
+        <v>3.408241898012285</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.448083673420919</v>
       </c>
       <c r="E18">
-        <v>-19.63203731914247</v>
+        <v>-20.22601008388454</v>
       </c>
       <c r="F18">
-        <v>-2.947497039888709</v>
+        <v>-2.701109924702232</v>
       </c>
       <c r="G18">
-        <v>2.657764398078282</v>
+        <v>3.632574395389919</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.352719685551843</v>
       </c>
       <c r="E19">
-        <v>-21.27060676865588</v>
+        <v>-20.95194258121013</v>
       </c>
       <c r="F19">
-        <v>-2.579598367120378</v>
+        <v>-2.283597843078031</v>
       </c>
       <c r="G19">
-        <v>2.445194269001679</v>
+        <v>3.87744882783873</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.227674590646491</v>
       </c>
       <c r="E20">
-        <v>-22.93064571343967</v>
+        <v>-22.146214388883</v>
       </c>
       <c r="F20">
-        <v>-2.043690217716252</v>
+        <v>-2.047664724514884</v>
       </c>
       <c r="G20">
-        <v>2.966323795066053</v>
+        <v>4.923584528793964</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.112807238797316</v>
       </c>
       <c r="E21">
-        <v>-21.31932862050441</v>
+        <v>-23.59360072274059</v>
       </c>
       <c r="F21">
-        <v>-2.173835848737485</v>
+        <v>-1.962324657943674</v>
       </c>
       <c r="G21">
-        <v>3.892329730037754</v>
+        <v>4.542173266668992</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.051643976549488</v>
       </c>
       <c r="E22">
-        <v>-22.25631517743148</v>
+        <v>-23.17847551045745</v>
       </c>
       <c r="F22">
-        <v>-2.304094137725499</v>
+        <v>-1.629768280415784</v>
       </c>
       <c r="G22">
-        <v>5.281322079767609</v>
+        <v>5.385643990801122</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.075153203058446</v>
       </c>
       <c r="E23">
-        <v>-23.31893971722736</v>
+        <v>-23.95914367311374</v>
       </c>
       <c r="F23">
-        <v>-2.011349925943557</v>
+        <v>-1.741160501805039</v>
       </c>
       <c r="G23">
-        <v>3.941878665124026</v>
+        <v>5.291339790569443</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.206148631165893</v>
       </c>
       <c r="E24">
-        <v>-25.43503675084962</v>
+        <v>-23.34693927201679</v>
       </c>
       <c r="F24">
-        <v>-1.443741812769099</v>
+        <v>-1.506778087019933</v>
       </c>
       <c r="G24">
-        <v>3.856761228763824</v>
+        <v>4.919578768691446</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.4631998803440309</v>
       </c>
       <c r="E25">
-        <v>-24.82335312426355</v>
+        <v>-24.23971886568098</v>
       </c>
       <c r="F25">
-        <v>-1.764922220754343</v>
+        <v>-1.361765746220657</v>
       </c>
       <c r="G25">
-        <v>3.365582208193237</v>
+        <v>4.91896962831222</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.1376183640055864</v>
       </c>
       <c r="E26">
-        <v>-24.94477962630522</v>
+        <v>-25.13994327061379</v>
       </c>
       <c r="F26">
-        <v>-2.184648528446227</v>
+        <v>-1.399649472652887</v>
       </c>
       <c r="G26">
-        <v>4.045217344132376</v>
+        <v>5.223930462298803</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.5932418179076486</v>
       </c>
       <c r="E27">
-        <v>-24.32753956211173</v>
+        <v>-25.43810705622682</v>
       </c>
       <c r="F27">
-        <v>-1.002850717935687</v>
+        <v>-1.229634518534914</v>
       </c>
       <c r="G27">
-        <v>3.503413461175253</v>
+        <v>5.193423785154419</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9095014703824719</v>
       </c>
       <c r="E28">
-        <v>-26.48103273408934</v>
+        <v>-25.8269218345254</v>
       </c>
       <c r="F28">
-        <v>-1.397041772068874</v>
+        <v>-1.12529998741751</v>
       </c>
       <c r="G28">
-        <v>3.868477249427305</v>
+        <v>4.444687632174073</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.092776010278034</v>
       </c>
       <c r="E29">
-        <v>-24.54213941686123</v>
+        <v>-24.33617536204437</v>
       </c>
       <c r="F29">
-        <v>-1.435648663243748</v>
+        <v>-1.078734970603942</v>
       </c>
       <c r="G29">
-        <v>3.822262033699079</v>
+        <v>4.364499598121846</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.153798566028264</v>
       </c>
       <c r="E30">
-        <v>-25.68200613780594</v>
+        <v>-25.14091236405143</v>
       </c>
       <c r="F30">
-        <v>-1.094625542491845</v>
+        <v>-1.037768060698492</v>
       </c>
       <c r="G30">
-        <v>3.179089246329473</v>
+        <v>4.886506418754127</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.109566771290343</v>
       </c>
       <c r="E31">
-        <v>-23.52438299753334</v>
+        <v>-24.39319790674895</v>
       </c>
       <c r="F31">
-        <v>-1.136349580203453</v>
+        <v>-0.9738214106719814</v>
       </c>
       <c r="G31">
-        <v>2.245333324250338</v>
+        <v>4.760864594447707</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.9802375648745353</v>
       </c>
       <c r="E32">
-        <v>-23.7197730655423</v>
+        <v>-23.99842365665628</v>
       </c>
       <c r="F32">
-        <v>-1.015059196718146</v>
+        <v>-0.9081285621603694</v>
       </c>
       <c r="G32">
-        <v>3.044048783237062</v>
+        <v>3.122098204870919</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.7797406410821602</v>
       </c>
       <c r="E33">
-        <v>-22.22997304412887</v>
+        <v>-23.16709545527617</v>
       </c>
       <c r="F33">
-        <v>-1.094589922693524</v>
+        <v>-0.993894409576619</v>
       </c>
       <c r="G33">
-        <v>3.332334399342336</v>
+        <v>3.082709334044671</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.5216443081862492</v>
       </c>
       <c r="E34">
-        <v>-23.35682945924954</v>
+        <v>-24.09087245352287</v>
       </c>
       <c r="F34">
-        <v>-1.37511737201898</v>
+        <v>-1.083756533799712</v>
       </c>
       <c r="G34">
-        <v>2.393433889495174</v>
+        <v>3.391222383394892</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.2186527236089383</v>
       </c>
       <c r="E35">
-        <v>-24.04671077500007</v>
+        <v>-22.28489437689389</v>
       </c>
       <c r="F35">
-        <v>-0.6602313331985893</v>
+        <v>-0.6917954447148617</v>
       </c>
       <c r="G35">
-        <v>1.025784626857001</v>
+        <v>2.700480367171498</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.1176900030665523</v>
       </c>
       <c r="E36">
-        <v>-21.10178525764993</v>
+        <v>-22.04300593777418</v>
       </c>
       <c r="F36">
-        <v>-1.279559393534237</v>
+        <v>-0.8326452393150701</v>
       </c>
       <c r="G36">
-        <v>2.028777298344453</v>
+        <v>2.802186947228988</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.4822111274070155</v>
       </c>
       <c r="E37">
-        <v>-21.12549181908009</v>
+        <v>-22.21598005944517</v>
       </c>
       <c r="F37">
-        <v>-0.4943449622161687</v>
+        <v>-0.5103175424769488</v>
       </c>
       <c r="G37">
-        <v>1.040513243961218</v>
+        <v>2.905489210236405</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8696312584412248</v>
       </c>
       <c r="E38">
-        <v>-21.32076867523885</v>
+        <v>-21.25099394772866</v>
       </c>
       <c r="F38">
-        <v>-0.9212457599836995</v>
+        <v>-0.4784394797150154</v>
       </c>
       <c r="G38">
-        <v>2.218004770823654</v>
+        <v>1.986624121992913</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.273756196570438</v>
       </c>
       <c r="E39">
-        <v>-20.00219025605543</v>
+        <v>-20.21036873466205</v>
       </c>
       <c r="F39">
-        <v>-0.6506752868398942</v>
+        <v>-0.7388185487021784</v>
       </c>
       <c r="G39">
-        <v>1.337926034118263</v>
+        <v>2.683798528199111</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.688302118232507</v>
       </c>
       <c r="E40">
-        <v>-20.01723837518292</v>
+        <v>-20.43074692224533</v>
       </c>
       <c r="F40">
-        <v>-0.5540197215464423</v>
+        <v>-0.5699310026194152</v>
       </c>
       <c r="G40">
-        <v>1.883076878615588</v>
+        <v>2.469348009256202</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.110137259599567</v>
       </c>
       <c r="E41">
-        <v>-18.28044179596912</v>
+        <v>-19.411550448183</v>
       </c>
       <c r="F41">
-        <v>-0.05092154823239896</v>
+        <v>-0.1893781894059195</v>
       </c>
       <c r="G41">
-        <v>0.2991298126235927</v>
+        <v>2.189113639902435</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.535628213459763</v>
       </c>
       <c r="E42">
-        <v>-19.50859111769337</v>
+        <v>-18.45487861474459</v>
       </c>
       <c r="F42">
-        <v>-0.6765162079702248</v>
+        <v>-0.3313297126518512</v>
       </c>
       <c r="G42">
-        <v>1.004315739034827</v>
+        <v>2.343951165319687</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.95870464351806</v>
       </c>
       <c r="E43">
-        <v>-16.02012645062459</v>
+        <v>-17.59968988381806</v>
       </c>
       <c r="F43">
-        <v>-0.5076949312796856</v>
+        <v>0.2196679773616707</v>
       </c>
       <c r="G43">
-        <v>1.553224052719225</v>
+        <v>1.453185987613528</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.37439303280632</v>
       </c>
       <c r="E44">
-        <v>-16.87842624319438</v>
+        <v>-17.29338390193924</v>
       </c>
       <c r="F44">
-        <v>0.05823656627150589</v>
+        <v>-0.1171238426967326</v>
       </c>
       <c r="G44">
-        <v>0.301635895596821</v>
+        <v>1.104489536507634</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.782188892990414</v>
       </c>
       <c r="E45">
-        <v>-16.47470372846255</v>
+        <v>-17.2760036186978</v>
       </c>
       <c r="F45">
-        <v>-0.2094487032083487</v>
+        <v>0.06754824424637514</v>
       </c>
       <c r="G45">
-        <v>-0.4675561182706822</v>
+        <v>2.258290799491045</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.182551365561841</v>
       </c>
       <c r="E46">
-        <v>-14.6226891850716</v>
+        <v>-15.77476467194099</v>
       </c>
       <c r="F46">
-        <v>-0.2350866743249934</v>
+        <v>-0.2963726082537121</v>
       </c>
       <c r="G46">
-        <v>0.4056433048041039</v>
+        <v>1.613062163341552</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.573408901126815</v>
       </c>
       <c r="E47">
-        <v>-14.87750641748321</v>
+        <v>-14.91816305712408</v>
       </c>
       <c r="F47">
-        <v>-0.7447430323670005</v>
+        <v>0.3741361320639029</v>
       </c>
       <c r="G47">
-        <v>0.29373693394012</v>
+        <v>2.01452871034343</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.95652368761406</v>
       </c>
       <c r="E48">
-        <v>-13.27159632251311</v>
+        <v>-14.93740907165667</v>
       </c>
       <c r="F48">
-        <v>0.102981659901124</v>
+        <v>0.4579544877161709</v>
       </c>
       <c r="G48">
-        <v>0.7913185495836579</v>
+        <v>0.5227339899825865</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.339363639234072</v>
       </c>
       <c r="E49">
-        <v>-14.41423899802453</v>
+        <v>-14.07444495085898</v>
       </c>
       <c r="F49">
-        <v>-0.4370136542684149</v>
+        <v>-0.1869063410759658</v>
       </c>
       <c r="G49">
-        <v>0.4304757068941771</v>
+        <v>1.106333510373008</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.72830837657741</v>
       </c>
       <c r="E50">
-        <v>-13.03429069908916</v>
+        <v>-14.33830554586391</v>
       </c>
       <c r="F50">
-        <v>0.001329382433985454</v>
+        <v>0.4668818032161412</v>
       </c>
       <c r="G50">
-        <v>-0.03092826709620534</v>
+        <v>1.362854442028975</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.122967225474522</v>
       </c>
       <c r="E51">
-        <v>-13.11422732227256</v>
+        <v>-12.96430766177462</v>
       </c>
       <c r="F51">
-        <v>-0.1618200626495856</v>
+        <v>0.2875559994907014</v>
       </c>
       <c r="G51">
-        <v>-0.7914168567409646</v>
+        <v>1.026340798507598</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.527476793432442</v>
       </c>
       <c r="E52">
-        <v>-11.7910751443414</v>
+        <v>-11.587751189871</v>
       </c>
       <c r="F52">
-        <v>0.3828687812242154</v>
+        <v>0.5550457742634954</v>
       </c>
       <c r="G52">
-        <v>1.306614894407836</v>
+        <v>0.8803126347703459</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.948897055783119</v>
       </c>
       <c r="E53">
-        <v>-9.113257137859691</v>
+        <v>-11.43429479117308</v>
       </c>
       <c r="F53">
-        <v>0.04586324237588968</v>
+        <v>0.09816636018865046</v>
       </c>
       <c r="G53">
-        <v>-0.3839184957665349</v>
+        <v>1.733844106796322</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.389520450603368</v>
       </c>
       <c r="E54">
-        <v>-10.06703980488121</v>
+        <v>-10.33202798991405</v>
       </c>
       <c r="F54">
-        <v>0.1584847609908993</v>
+        <v>0.6897267168150558</v>
       </c>
       <c r="G54">
-        <v>-1.063686053527245</v>
+        <v>0.7728854320209959</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.84056752625896</v>
       </c>
       <c r="E55">
-        <v>-7.665395314231293</v>
+        <v>-9.491534157142418</v>
       </c>
       <c r="F55">
-        <v>-0.5049505500742107</v>
+        <v>0.8021916739909363</v>
       </c>
       <c r="G55">
-        <v>-0.1326811947912445</v>
+        <v>1.230813333195144</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.302456830077475</v>
       </c>
       <c r="E56">
-        <v>-9.434384815165618</v>
+        <v>-10.0116520392934</v>
       </c>
       <c r="F56">
-        <v>0.0595503569723459</v>
+        <v>0.5440226892344424</v>
       </c>
       <c r="G56">
-        <v>0.04576714141209025</v>
+        <v>0.1932982928241714</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.776355424528981</v>
       </c>
       <c r="E57">
-        <v>-9.522563261042976</v>
+        <v>-9.785708357154693</v>
       </c>
       <c r="F57">
-        <v>-0.3148352609273075</v>
+        <v>0.1286718181641451</v>
       </c>
       <c r="G57">
-        <v>-0.4083403902097385</v>
+        <v>0.7552667086609947</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.258360518148223</v>
       </c>
       <c r="E58">
-        <v>-8.984553378087691</v>
+        <v>-8.628162473684034</v>
       </c>
       <c r="F58">
-        <v>-0.3520140466997549</v>
+        <v>0.5861385447275749</v>
       </c>
       <c r="G58">
-        <v>-0.198815963029265</v>
+        <v>0.3405977060485036</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.731944596818366</v>
       </c>
       <c r="E59">
-        <v>-8.03807513964054</v>
+        <v>-8.377606535313641</v>
       </c>
       <c r="F59">
-        <v>0.1271235994883128</v>
+        <v>0.4941591134229261</v>
       </c>
       <c r="G59">
-        <v>-1.862861678343927</v>
+        <v>0.03121398322145411</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.19601482222491</v>
       </c>
       <c r="E60">
-        <v>-6.570097834470071</v>
+        <v>-7.51564773574565</v>
       </c>
       <c r="F60">
-        <v>0.07856718743841416</v>
+        <v>0.4470241798362314</v>
       </c>
       <c r="G60">
-        <v>-1.549174246315825</v>
+        <v>-0.51803200610795</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.64658253611889</v>
       </c>
       <c r="E61">
-        <v>-6.881557219769623</v>
+        <v>-8.466473309240163</v>
       </c>
       <c r="F61">
-        <v>-0.2553303169146078</v>
+        <v>0.6828786034961123</v>
       </c>
       <c r="G61">
-        <v>-0.599994492569226</v>
+        <v>-0.7254873423263789</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.07520954827292</v>
       </c>
       <c r="E62">
-        <v>-6.393052614666191</v>
+        <v>-7.463511414495341</v>
       </c>
       <c r="F62">
-        <v>-0.3254897224621147</v>
+        <v>0.7002411842587899</v>
       </c>
       <c r="G62">
-        <v>-1.073289946136671</v>
+        <v>-1.035417305167408</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.46231292570966</v>
       </c>
       <c r="E63">
-        <v>-7.024380761497539</v>
+        <v>-7.519936200630913</v>
       </c>
       <c r="F63">
-        <v>0.2360149796885162</v>
+        <v>0.2254822881619205</v>
       </c>
       <c r="G63">
-        <v>-0.01790458094471249</v>
+        <v>-0.04628919839842365</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.80703615906928</v>
       </c>
       <c r="E64">
-        <v>-5.566189488657645</v>
+        <v>-6.245193409841746</v>
       </c>
       <c r="F64">
-        <v>0.1247768346361818</v>
+        <v>0.2429906615874908</v>
       </c>
       <c r="G64">
-        <v>-1.56509465981418</v>
+        <v>0.4319654523868491</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.10492647703825</v>
       </c>
       <c r="E65">
-        <v>-7.247113755564805</v>
+        <v>-6.84564189241479</v>
       </c>
       <c r="F65">
-        <v>0.5002443003638913</v>
+        <v>0.5919644526714638</v>
       </c>
       <c r="G65">
-        <v>-1.429805905806324</v>
+        <v>-1.006916818619823</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.34706020028754</v>
       </c>
       <c r="E66">
-        <v>-6.724056893782848</v>
+        <v>-7.67601458577928</v>
       </c>
       <c r="F66">
-        <v>0.03147532895666506</v>
+        <v>0.3451200786786419</v>
       </c>
       <c r="G66">
-        <v>-1.691948143787974</v>
+        <v>-0.6725715824266683</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.5171249736982</v>
       </c>
       <c r="E67">
-        <v>-4.73677683178278</v>
+        <v>-5.546024193901489</v>
       </c>
       <c r="F67">
-        <v>-0.2532030694242187</v>
+        <v>-0.04076659224147982</v>
       </c>
       <c r="G67">
-        <v>-1.081688800169802</v>
+        <v>-0.9932773709980253</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.61770048140483</v>
       </c>
       <c r="E68">
-        <v>-5.794614774552553</v>
+        <v>-6.967783893349674</v>
       </c>
       <c r="F68">
-        <v>0.1776904592248058</v>
+        <v>-0.2401049240511529</v>
       </c>
       <c r="G68">
-        <v>-0.9762048876520037</v>
+        <v>-0.4465970544615563</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.64804692409137</v>
       </c>
       <c r="E69">
-        <v>-5.75278978861771</v>
+        <v>-5.601914620104156</v>
       </c>
       <c r="F69">
-        <v>-0.4608557248557903</v>
+        <v>0.372446262562192</v>
       </c>
       <c r="G69">
-        <v>-1.441869533751428</v>
+        <v>-0.9133872860443329</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.6038122541837</v>
       </c>
       <c r="E70">
-        <v>-4.888453540195692</v>
+        <v>-6.699865785633873</v>
       </c>
       <c r="F70">
-        <v>-0.1199808818689881</v>
+        <v>-0.03937576337217946</v>
       </c>
       <c r="G70">
-        <v>-2.240038752724172</v>
+        <v>-0.9757182374577309</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.47695824395814</v>
       </c>
       <c r="E71">
-        <v>-4.721348320838648</v>
+        <v>-6.162598572415846</v>
       </c>
       <c r="F71">
-        <v>-0.3653259108627429</v>
+        <v>-0.0478507902702212</v>
       </c>
       <c r="G71">
-        <v>-1.402384657104541</v>
+        <v>-0.215454764909642</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.27938578917924</v>
       </c>
       <c r="E72">
-        <v>-6.188438045103613</v>
+        <v>-6.9609504260721</v>
       </c>
       <c r="F72">
-        <v>-0.5531275698536272</v>
+        <v>0.2916125146622106</v>
       </c>
       <c r="G72">
-        <v>-1.269866829713054</v>
+        <v>-0.6852410402054591</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.01833188060731</v>
       </c>
       <c r="E73">
-        <v>-4.771641553167835</v>
+        <v>-6.532977933029197</v>
       </c>
       <c r="F73">
-        <v>-0.2809658029290441</v>
+        <v>0.03170312999243493</v>
       </c>
       <c r="G73">
-        <v>-1.393466047421744</v>
+        <v>-1.314986254867781</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.69766793844531</v>
       </c>
       <c r="E74">
-        <v>-4.628079870176669</v>
+        <v>-7.04210520876356</v>
       </c>
       <c r="F74">
-        <v>-0.6715691978407061</v>
+        <v>-0.2555009605995844</v>
       </c>
       <c r="G74">
-        <v>-1.815219617488276</v>
+        <v>-0.7466615915955575</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.31829428002594</v>
       </c>
       <c r="E75">
-        <v>-5.782890555346694</v>
+        <v>-6.278717702920529</v>
       </c>
       <c r="F75">
-        <v>-1.015722719007789</v>
+        <v>-0.2470922030937667</v>
       </c>
       <c r="G75">
-        <v>-0.96890844528345</v>
+        <v>-0.06230230717187838</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.899626475033</v>
       </c>
       <c r="E76">
-        <v>-7.552536685012132</v>
+        <v>-7.405673744469374</v>
       </c>
       <c r="F76">
-        <v>-0.4443571312942325</v>
+        <v>-0.05583708040061123</v>
       </c>
       <c r="G76">
-        <v>-1.810667617371778</v>
+        <v>0.1871704730309805</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.45142322597809</v>
       </c>
       <c r="E77">
-        <v>-7.875448581077082</v>
+        <v>-7.697253128875253</v>
       </c>
       <c r="F77">
-        <v>-1.663573125756629</v>
+        <v>-0.3037028314010849</v>
       </c>
       <c r="G77">
-        <v>0.1820027114441782</v>
+        <v>-0.1768405617395829</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.977988474433642</v>
       </c>
       <c r="E78">
-        <v>-7.795933105976398</v>
+        <v>-7.790014390448373</v>
       </c>
       <c r="F78">
-        <v>-0.9660852874972368</v>
+        <v>-0.1785240913270376</v>
       </c>
       <c r="G78">
-        <v>0.2714668940974427</v>
+        <v>0.4056399942585646</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.478361047171575</v>
       </c>
       <c r="E79">
-        <v>-9.353800620199124</v>
+        <v>-8.665585782883422</v>
       </c>
       <c r="F79">
-        <v>-1.198482933985235</v>
+        <v>-0.1581421113811558</v>
       </c>
       <c r="G79">
-        <v>0.1735608203190366</v>
+        <v>0.3078332368463367</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.967836957107393</v>
       </c>
       <c r="E80">
-        <v>-9.288577009066648</v>
+        <v>-9.197627137096596</v>
       </c>
       <c r="F80">
-        <v>-1.319514866840868</v>
+        <v>-0.5645126514377037</v>
       </c>
       <c r="G80">
-        <v>-0.3418911201454872</v>
+        <v>0.9157122982217728</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.448885252684468</v>
       </c>
       <c r="E81">
-        <v>-9.50859744720332</v>
+        <v>-9.652516879641091</v>
       </c>
       <c r="F81">
-        <v>-1.375779237573816</v>
+        <v>-0.7084663386962017</v>
       </c>
       <c r="G81">
-        <v>0.56101051750764</v>
+        <v>1.41402223388395</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.919594787540812</v>
       </c>
       <c r="E82">
-        <v>-11.76796181300625</v>
+        <v>-10.23532695595426</v>
       </c>
       <c r="F82">
-        <v>-1.086472750513492</v>
+        <v>-0.8408394496635627</v>
       </c>
       <c r="G82">
-        <v>0.5082106267018038</v>
+        <v>0.5106140827633147</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.376482566881462</v>
       </c>
       <c r="E83">
-        <v>-11.06823106628904</v>
+        <v>-11.68258649253964</v>
       </c>
       <c r="F83">
-        <v>-1.523186388534586</v>
+        <v>-0.8753674597470518</v>
       </c>
       <c r="G83">
-        <v>1.924597740769128</v>
+        <v>2.052543704770881</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.830028026178565</v>
       </c>
       <c r="E84">
-        <v>-12.03699845380194</v>
+        <v>-13.22482171448788</v>
       </c>
       <c r="F84">
-        <v>-1.746023846826875</v>
+        <v>-0.9823428261445799</v>
       </c>
       <c r="G84">
-        <v>1.06294218998978</v>
+        <v>1.281871877047323</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.281308237380651</v>
       </c>
       <c r="E85">
-        <v>-13.06174683699767</v>
+        <v>-13.792841794692</v>
       </c>
       <c r="F85">
-        <v>-1.038243543587699</v>
+        <v>-1.023487006674229</v>
       </c>
       <c r="G85">
-        <v>0.1224426866471502</v>
+        <v>2.115079910007713</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.730006480535023</v>
       </c>
       <c r="E86">
-        <v>-13.5935300681924</v>
+        <v>-14.08592010399442</v>
       </c>
       <c r="F86">
-        <v>-2.04575202418182</v>
+        <v>-1.108578563024599</v>
       </c>
       <c r="G86">
-        <v>0.3830422104074995</v>
+        <v>1.480312597762317</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.179602822758227</v>
       </c>
       <c r="E87">
-        <v>-17.65437120746068</v>
+        <v>-16.61779897863093</v>
       </c>
       <c r="F87">
-        <v>-1.688799398274082</v>
+        <v>-1.518836631302485</v>
       </c>
       <c r="G87">
-        <v>1.82324538908434</v>
+        <v>1.570035002967644</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.643753137588929</v>
       </c>
       <c r="E88">
-        <v>-15.80602472801594</v>
+        <v>-16.77031345473526</v>
       </c>
       <c r="F88">
-        <v>-2.05084731207644</v>
+        <v>-1.516349872359281</v>
       </c>
       <c r="G88">
-        <v>1.771355898301804</v>
+        <v>2.241221626690563</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.130257638653265</v>
       </c>
       <c r="E89">
-        <v>-18.11499399809889</v>
+        <v>-18.99740791475953</v>
       </c>
       <c r="F89">
-        <v>-1.997178216416463</v>
+        <v>-1.591843135613414</v>
       </c>
       <c r="G89">
-        <v>2.572471502804499</v>
+        <v>1.265266180622339</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.645406818611877</v>
       </c>
       <c r="E90">
-        <v>-19.54000967035859</v>
+        <v>-20.36951742518761</v>
       </c>
       <c r="F90">
-        <v>-2.250159136129223</v>
+        <v>-2.279547126478341</v>
       </c>
       <c r="G90">
-        <v>0.9612322993867516</v>
+        <v>2.214962379473064</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.202368376607063</v>
       </c>
       <c r="E91">
-        <v>-20.21195822903874</v>
+        <v>-20.38070275598656</v>
       </c>
       <c r="F91">
-        <v>-1.524414857392937</v>
+        <v>-1.655937235037623</v>
       </c>
       <c r="G91">
-        <v>0.6784885365142174</v>
+        <v>2.271115852910182</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.819345639592948</v>
       </c>
       <c r="E92">
-        <v>-22.59395367096938</v>
+        <v>-23.45626569150997</v>
       </c>
       <c r="F92">
-        <v>-2.389665318802091</v>
+        <v>-2.163384337216364</v>
       </c>
       <c r="G92">
-        <v>1.547082990743877</v>
+        <v>1.320976040957194</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.509196899966442</v>
       </c>
       <c r="E93">
-        <v>-23.36753024332967</v>
+        <v>-25.12753072335877</v>
       </c>
       <c r="F93">
-        <v>-2.687519729091903</v>
+        <v>-2.50715432427595</v>
       </c>
       <c r="G93">
-        <v>1.350674944989996</v>
+        <v>1.838030285462726</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.279239846720095</v>
       </c>
       <c r="E94">
-        <v>-26.94185024910987</v>
+        <v>-26.94237555209476</v>
       </c>
       <c r="F94">
-        <v>-2.614767533573634</v>
+        <v>-2.208228834934318</v>
       </c>
       <c r="G94">
-        <v>0.8368584140218723</v>
+        <v>1.967211082950626</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.141083581768995</v>
       </c>
       <c r="E95">
-        <v>-28.45834562479852</v>
+        <v>-28.10961689841584</v>
       </c>
       <c r="F95">
-        <v>-2.408393877411985</v>
+        <v>-2.465377271050563</v>
       </c>
       <c r="G95">
-        <v>0.9564253872637298</v>
+        <v>1.120115311452994</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.106206246455848</v>
       </c>
       <c r="E96">
-        <v>-30.60236749338908</v>
+        <v>-30.96808931848554</v>
       </c>
       <c r="F96">
-        <v>-3.826920039192359</v>
+        <v>-2.874770523759926</v>
       </c>
       <c r="G96">
-        <v>1.357315899341774</v>
+        <v>1.082980922138989</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.169966829086061</v>
       </c>
       <c r="E97">
-        <v>-32.80222997496822</v>
+        <v>-33.11290819850145</v>
       </c>
       <c r="F97">
-        <v>-3.142061490356048</v>
+        <v>-2.975194332368713</v>
       </c>
       <c r="G97">
-        <v>0.916288333145606</v>
+        <v>1.677508553354544</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.331830952284853</v>
       </c>
       <c r="E98">
-        <v>-34.46934466038899</v>
+        <v>-35.1613453019751</v>
       </c>
       <c r="F98">
-        <v>-3.505269946889728</v>
+        <v>-2.763604446671635</v>
       </c>
       <c r="G98">
-        <v>-0.2506160690822413</v>
+        <v>1.346566557975761</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.572555790527292</v>
       </c>
       <c r="E99">
-        <v>-36.79886188128174</v>
+        <v>-37.20792346686861</v>
       </c>
       <c r="F99">
-        <v>-3.493423464662292</v>
+        <v>-3.207938236431082</v>
       </c>
       <c r="G99">
-        <v>0.5406804573509756</v>
+        <v>-0.5602017351871864</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.899802972080086</v>
       </c>
       <c r="E100">
-        <v>-38.14068722178353</v>
+        <v>-40.58346157760812</v>
       </c>
       <c r="F100">
-        <v>-3.240595792919049</v>
+        <v>-3.333004318538348</v>
       </c>
       <c r="G100">
-        <v>-0.186265684889888</v>
+        <v>0.03082333884782011</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.262407399007325</v>
       </c>
       <c r="E101">
-        <v>-41.16637807306046</v>
+        <v>-42.85234932424918</v>
       </c>
       <c r="F101">
-        <v>-3.802826973281936</v>
+        <v>-3.17540079321652</v>
       </c>
       <c r="G101">
-        <v>-0.4951892418869788</v>
+        <v>-0.5126093325146238</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.691519538260803</v>
       </c>
       <c r="E102">
-        <v>-43.70886489805994</v>
+        <v>-43.95896798902957</v>
       </c>
       <c r="F102">
-        <v>-3.59886303789503</v>
+        <v>-3.74944532111073</v>
       </c>
       <c r="G102">
-        <v>-1.632590062268841</v>
+        <v>-0.7560205038350771</v>
       </c>
     </row>
   </sheetData>
